--- a/data/results/classified_articles_llm.xlsx
+++ b/data/results/classified_articles_llm.xlsx
@@ -645,7 +645,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>The abstract focuses on developing a data-driven approach to predict restoration times for outages, which directly relates to resilience in power systems. It addresses the need for methods that enhance recovery and adaptation to adverse conditions, particularly in the context of utilizing large datasets and advanced modeling techniques.</t>
+          <t>The abstract focuses on developing a data-driven approach to predict restoration times for outages, which directly relates to resilience concepts in power systems. By incorporating various factors such as weather information and outage-related features, the research addresses the need for methods that enhance recovery and adaptation to adverse conditions, aligning well with the objectives of RA2025 ID 46.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>The abstract discusses the need for a probabilistic framework and composite stability indices for assessing multiple aspects of power system stability in the context of integrating renewable energy sources. This aligns closely with RA2025 ID 9, which focuses on providing analytical tools and models for robust assessment of system performance in inverter-based resource (IBR)-dominated power grids.</t>
+          <t>The paper focuses on developing a probabilistic framework and composite stability indices for assessing multiple aspects of power system stability in the context of increased integration of renewable energy sources and the decline of traditional synchronous generation. This aligns closely with RA2025 ID 9, which seeks analytical tools and models for robust assessment of system performance in inverter-based resource (IBR) dominated power grids.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
